--- a/dataset_merge/output/merge_dataset.xlsx
+++ b/dataset_merge/output/merge_dataset.xlsx
@@ -9,6 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:AP485"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -69292,6 +69293,5 @@
       </c>
     </row>
   </sheetData>
-  <dimension ref="A1:AP485"/>
 </worksheet>
 </file>